--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -342,7 +342,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>九月金秋</t>
+    <t>中秋节</t>
   </si>
   <si>
     <t>1005</t>
@@ -351,10 +351,10 @@
     <t>50</t>
   </si>
   <si>
-    <t>2026-09-03</t>
-  </si>
-  <si>
-    <t>2026-09-08</t>
+    <t>2026-09-24</t>
+  </si>
+  <si>
+    <t>2026-09-28</t>
   </si>
   <si>
     <t>平时部分掉落</t>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -342,7 +342,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>中秋节</t>
+    <t>国庆节</t>
   </si>
   <si>
     <t>1005</t>
@@ -351,10 +351,10 @@
     <t>50</t>
   </si>
   <si>
-    <t>2026-09-24</t>
-  </si>
-  <si>
-    <t>2026-09-28</t>
+    <t>2026-10-01</t>
+  </si>
+  <si>
+    <t>2026-10-08</t>
   </si>
   <si>
     <t>平时部分掉落</t>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -366,7 +366,7 @@
     <t>2024-10-31</t>
   </si>
   <si>
-    <t>2026-10-21</t>
+    <t>2027-10-21</t>
   </si>
   <si>
     <t>第一批白图鉴</t>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -342,7 +342,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>国庆节</t>
+    <t>冬日快乐</t>
   </si>
   <si>
     <t>1005</t>
@@ -351,10 +351,10 @@
     <t>50</t>
   </si>
   <si>
-    <t>2026-10-01</t>
-  </si>
-  <si>
-    <t>2026-10-08</t>
+    <t>2026-10-30</t>
+  </si>
+  <si>
+    <t>2026-11-08</t>
   </si>
   <si>
     <t>平时部分掉落</t>
